--- a/05. Res/modelos/comparativo_prima_pura.xlsx
+++ b/05. Res/modelos/comparativo_prima_pura.xlsx
@@ -423,19 +423,19 @@
         <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>876859.179197354</v>
+        <v>5116509.53416436</v>
       </c>
       <c r="D2" t="n">
-        <v>10204.4136134476</v>
+        <v>35443.9695176813</v>
       </c>
       <c r="E2" t="n">
-        <v>148.814915726359</v>
+        <v>146.95652310875</v>
       </c>
       <c r="F2" t="n">
-        <v>10179.3945696783</v>
+        <v>35423.2685020443</v>
       </c>
       <c r="G2" t="n">
-        <v>10030.5796539519</v>
+        <v>35276.3119789356</v>
       </c>
     </row>
     <row r="3">
@@ -446,19 +446,19 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>876859.179197354</v>
+        <v>5116509.53416436</v>
       </c>
       <c r="D3" t="n">
-        <v>10204.4136134476</v>
+        <v>35443.9695176813</v>
       </c>
       <c r="E3" t="n">
-        <v>148.814915726359</v>
+        <v>146.95652310875</v>
       </c>
       <c r="F3" t="n">
-        <v>10179.3945696783</v>
+        <v>35423.2685020443</v>
       </c>
       <c r="G3" t="n">
-        <v>10030.5796539519</v>
+        <v>35276.3119789356</v>
       </c>
     </row>
     <row r="4">
@@ -469,19 +469,19 @@
         <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>3931.16536192832</v>
+        <v>6557.1205358141</v>
       </c>
       <c r="D4" t="n">
-        <v>249.891862064498</v>
+        <v>250.925878517657</v>
       </c>
       <c r="E4" t="n">
-        <v>148.814915726359</v>
+        <v>146.95652310875</v>
       </c>
       <c r="F4" t="n">
-        <v>205.06188075557</v>
+        <v>210.942157555913</v>
       </c>
       <c r="G4" t="n">
-        <v>56.2469650292114</v>
+        <v>63.9856344471631</v>
       </c>
     </row>
     <row r="5">
@@ -492,19 +492,19 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>910.178545612985</v>
+        <v>989.509574255253</v>
       </c>
       <c r="D5" t="n">
-        <v>160.519010932482</v>
+        <v>158.139021497238</v>
       </c>
       <c r="E5" t="n">
-        <v>148.814915726359</v>
+        <v>146.95652310875</v>
       </c>
       <c r="F5" t="n">
-        <v>65.5934249235052</v>
+        <v>65.9850486111818</v>
       </c>
       <c r="G5" t="n">
-        <v>-83.2214908028533</v>
+        <v>-80.9714744975681</v>
       </c>
     </row>
   </sheetData>
